--- a/Result/checksun_type/輸送機械及零配件.xlsx
+++ b/Result/checksun_type/輸送機械及零配件.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>154.3</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>152.7</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>151.28</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>151.28</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3403.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>5532.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>5532.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6606.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5934.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5934.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-489.1674751556511</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3403</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3403.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>154.1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>152.4</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>151.23</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>151.23</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1707.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>5713.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>5713.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>6826.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>5967.38</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>5967.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-313.2917090564597</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1707</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1707.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>153.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>152.1</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>151.2</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>152.1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>151.2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>7851.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>6656.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>6656.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>7009.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>5990.92</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>5990.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>130.8626606944026</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>7851</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>7851.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>153.9</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>151.78</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>151.16</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>151.78</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>151.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>10241.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6535.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6535.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>7713.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>5946.78</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>5946.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>102.409522456549</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>10241</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>10241.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>154.1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>151.57</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>151.14</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>151.57</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>151.14</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>4459.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>6984.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>6984.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>7280.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>5994.16</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>5994.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-197.966729399549</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>4459</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4459.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>154.1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>151.38</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>151.12</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>151.38</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>151.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>4311.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7681.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7681.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>7473.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6115.16</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>6115.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-0.505420286847766</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>4311</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>4311.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>154.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>151.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>151.13</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>151.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>151.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>6420.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7938.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7938.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>8035.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6145.76</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>6145.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>297.4573577415422</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>6420</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>6420.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,21 +4067,17 @@
           <t>154.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>150.98</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AM9" t="n">
+        <v>150.98</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>151.16</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>151.16</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>151.16</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
           <t>131.10</t>
@@ -4164,20 +4118,16 @@
           <t>7247.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7363.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7363</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>8085.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>6388.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>6388.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>486.5307064341878</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7247</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7247.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>153.6</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>150.75</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>151.15</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>150.75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>151.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>12486.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>8892.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>8892</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>8745.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>6567.28</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>6567.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>650.6522507653181</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>12486</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>12486.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>152.9</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>150.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>151.1</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>151.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>7942.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>7575.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>7575.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>7749.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>6515.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>6515</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>300.5525908538848</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>7942</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>7942.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>152.3</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>150.3</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>151.08</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>151.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5598.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>7266.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>7266.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>7945.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>6869.06</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>6869.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>276.5333413070557</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5598</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5598.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>56.84</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>56.96</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>57.83</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>57.83</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>184.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>360.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>360.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>546.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>1090.2</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>1090.2</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-172.6035522230702</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>184</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>184.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>56.77999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>56.92</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>57.95</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>57.95</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>448.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>416.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>416.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>533.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>1242.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>1242.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-158.5223552741121</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>448</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>448.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>56.77999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>56.91</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>58.14</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>58.14</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>227.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>690.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>690.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>770.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1379.6</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1379.6</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-161.0305612300966</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>227</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>227.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>56.96</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>56.92</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>58.28</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>58.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>576.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>656.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>656.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>772.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1412.84</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1412.84</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-135.184049694714</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>576</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>576.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>56.82000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>56.87</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>58.41</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>58.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>366.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>735.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>735.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>844.2</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1445.8</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1445.8</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-130.8253171550704</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>366</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>366.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>56.7</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>56.79</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>58.53</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>58.53</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>467.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>732.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>732</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>1309.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1566.66</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1566.66</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-97.42622362861277</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>467</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>467.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>57.02</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>56.79</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>58.68</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>56.79</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>58.68</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1815.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>650.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>650.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1366.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1587.08</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1587.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-57.05515346122297</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1815</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1815.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>57.27999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>56.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>58.81</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>58.81</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>57.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>851.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>851.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>1302.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1596.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1596.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-141.7730834556222</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>57</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>57.6</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>56.73</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>58.92</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>56.73</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>58.92</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>972.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>889.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>889.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>1381.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1649.92</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1649.92</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-69.37823046706308</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>972</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>972.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>58.06</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>56.76</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>59.08</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>59.08</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>349.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>953.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>953</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>1306.9</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1809.26</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1809.26</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-61.51493225244076</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>349</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>349.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>58.22000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>56.77</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>59.16</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>56.77</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>59.16</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>58.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1886.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1886.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1647.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1908.48</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1908.48</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>18.66531277746412</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>58</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>58.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>20.51</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>22.97</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>10516.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>6553.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>6553.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>6621.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>7055.1</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>7055.1</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>451.8476631753983</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>10516</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>10516.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>20.33</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>23.05</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>5964.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>5690.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>5690.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>6322.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>7140.5</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>7140.5</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>126.0489308279157</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>5964</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>5964.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>20.37</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>23.16</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>7205.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>5879.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>5879.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>5999.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>7311.98</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>7311.98</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>143.8347085162286</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>7205</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>7205.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>20.5</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23.27</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>7576.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>6293.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>6293</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>5560.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>7585.92</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>7585.92</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>31.14172276681074</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>7576</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>7576.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>20.82</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1505.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>6001.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>6001.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>5125.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>7728.1</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>7728.1</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-170.7104612597432</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1505</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1505.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>21.2</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>23.48</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>23.48</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>6204.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>6690.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>6690.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>5272.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>8019.26</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>8019.26</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>197.4903637473135</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>6204</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>6204.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>21.64</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>6909.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>6954.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>6954.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>5247.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>8221.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>8221.299999999999</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>212.9740293378472</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>6909</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>6909.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>23.71</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>9271.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>6118.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>6118.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>5174.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>8359.92</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>8359.92</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>151.9516219908282</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>9271</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>9271.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>23.8</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>6118.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>4827.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>4827</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>4621.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>8529.86</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>8529.860000000001</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-193.7215178617271</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>6118</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>6118.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>22.18</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>23.89</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>4949.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>4249.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>4249</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>4420.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>8793.4</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>8793.4</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-342.8002348703167</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>4949</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>4949.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>23.99</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>7524.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>3854.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>3854.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>4442.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>9497.76</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>9497.76</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-418.2769650657883</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>7524</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>7524.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>62.06</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>65.53</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>71.05</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>71.05</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>64137.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>56110.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>56110.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>66072.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>131071.42</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>131071.42</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-5046.292096739809</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>64137</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>64137.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>61.86</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>71.32</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>71.31999999999999</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>40116.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>54394.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>54394</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>68178.5</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>133670.02</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>133670.02</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-6045.859222618266</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>40116</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>40116.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>61.88</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>66.34</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>71.65</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>66.34</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>71.65000000000001</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>66567.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>63069.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>63069.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>68814.2</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>136082.22</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>136082.22</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-4684.210144493976</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>66567</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>66567.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>62.21999999999999</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>66.79</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>71.95</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>71.95</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>68921.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>61337.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>61337.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>67514.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>137842.84</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>137842.84</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-5405.739670584488</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>68921</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>68921.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>67.37</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>72.27</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>67.37</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>72.27</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>40813.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>60219.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>60219.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>67201.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>138237.78</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>138237.78</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-6495.648291050042</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>40813</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>40813.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>63.46</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>67.95</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>72.53</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>72.53</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>55553.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>76033.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>76033.39999999999</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>67880.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>139203.84</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>139203.84</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-4809.101738463331</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>55553</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>55553.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>64.3</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>68.54</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>72.82</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>68.54000000000001</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>72.81999999999999</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>83495.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>81963.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>81963</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>70377.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>140394.08</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>140394.08</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-3807.281601251496</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>83495</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>83495.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>65.36</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>69.04</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>73.11</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>73.11</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>57904.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>74558.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>74558.60000000001</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>72860.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>140798.66</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>140798.66</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-5233.921348047021</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>57904</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>57904.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>66.03999999999999</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>69.52</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>73.37</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>73.37</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>63333.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>73690.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>73690.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>76070.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>142749.4</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>142749.4</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-4343.159509610385</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>63333</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>63333.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>66.62</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>70.02</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>73.62</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>73.62</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>119882.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>74184.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>74184.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>74218.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>146686.82</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>146686.82</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-3497.208329357687</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>119882</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>119882.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>67.26</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>73.91</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>73.91</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>85201.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>59728.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>59728.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>69820.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>148731.72</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>148731.72</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-8222.627774376771</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>85201</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>85201.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>13.76</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>14.76</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>14.76</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>2035612.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1742622.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>1742622</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>3623289.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>4611435.6</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>4611435.6</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-730389.703553101</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>2035612</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>2035612.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>13.67</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>14.79</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>14.79</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>1130737.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>2006755.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>2006755.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>3720577.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>4673421.5</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>4673421.5</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-747155.6479886342</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>1130737</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>1130737.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>14.83</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>14.83</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>1144970.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>3164286.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>3164286.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>3982209.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>4788813.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>4788813.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-647471.9740398023</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>1144970</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>1144970.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>13.61</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>14.87</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>14.87</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>1478293.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>5213697.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>5213697.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>4243254.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>4943161.66</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>4943161.66</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-483467.6907543349</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>1478293</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>1478293.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>13.69</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>14.92</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>14.92</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>2923498.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>5645358.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>5645358.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>4277998.2</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>5044708.62</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>5044708.62</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-267622.3328195838</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>2923498</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>2923498.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>13.77</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>14.97</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>3356279.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>5503956.6</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>5503956.6</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>4189681.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>5444701.66</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>5444701.66</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-104557.2738835253</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>3356279</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>3356279.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>13.9</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>14.27</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>15.02</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>15.02</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>6918391.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>5434398.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>5434398.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>4271440.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>5617822.56</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>5617822.56</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>85757.60580668412</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>6918391</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>6918391.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>15.06</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>15.06</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>11392026.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>4800132.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>4800132</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>4131465.3</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>5585222.04</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>5585222.04</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-27081.62341468502</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>11392026</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>11392026.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>14.03</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>15.1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>3636599.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>3272812.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>3272812.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>4238385.9</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>5473025.66</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>5473025.66</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-666631.3571804017</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>3636599</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>3636599.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,21 +23847,17 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>14.48</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AM55" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="AO55" t="inlineStr">
         <is>
           <t>15.13</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>15.13</t>
-        </is>
-      </c>
       <c r="AP55" t="inlineStr">
         <is>
           <t>0.55</t>
@@ -24220,20 +23898,16 @@
           <t>2216488.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>2910637.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>2910637.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4261119.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>5563641.26</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>5563641.26</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-725526.9640892674</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>2216488</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>2216488.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>13.98</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>15.16</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>3008489.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>2875406.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>2875406.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>6471977.8</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>6141477.24</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>6141477.24</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-631597.118098746</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>3008489</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>3008489.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>58.23999999999999</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>61.05</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>65.24</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>65.23999999999999</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>60308512.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>50349341.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>50349341</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>60567771.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>170064514.82</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>170064514.82</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-15999065.95658765</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>60308512</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>60308512.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>57.86</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>61.33</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>65.56</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>65.56</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>34191922.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>51556202.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>51556202.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>63075503.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>186878910.32</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>186878910.32</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-17679761.73594396</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>34191922</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>34191922.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>57.96</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>61.75</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>65.94</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>65.94</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>35097496.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>61362092.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>61362092.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>97949354.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>200474560.72</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>200474560.72</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-16651129.57302642</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>35097496</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>35097496.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>58.6</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>62.14</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>66.29</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>62.14</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>66.29000000000001</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>64787676.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>69236476.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>69236476.59999999</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>121676634.5</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>214821835.84</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>214821835.84</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-14683997.64125042</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>64787676</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>64787676.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>59.62</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>62.58</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>66.64</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>66.64</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>57361099.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>67057623.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>67057623.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>122563213.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>218628587.54</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>218628587.54</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-14530471.39438291</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>57361099</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>57361099.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>60.4</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>62.97</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>66.93</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>62.97</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>66.93000000000001</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>66342820.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>70786202.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>70786202</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>120335298.0</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>223241961.6</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>223241961.6</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-12996498.09905848</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>66342820</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>66342820.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>61.86</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>63.5</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>67.25</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>67.25</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>83221372.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>74594804.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>74594804.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>122854430.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>235962436.6</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>235962436.6</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-11303274.28077151</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>83221372</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>83221372.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>63.26000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>67.61</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>67.61</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>74469416.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>134536616.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>134536616.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>123012790.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>275866481.28</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>275866481.28</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-10289111.03033401</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>74469416</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>74469416.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>63.82000000000001</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>63.88</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>67.88</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>67.88</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>53893409.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>174116792.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>174116792.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>121158820.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>294969414.14</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>294969414.14</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-7535128.564339936</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>53893409</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>53893409.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>63.44</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>63.95</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>68.06</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>68.06</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>76003993.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>178068803.2</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>178068803.2</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>123816223.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>330531577.32</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>330531577.32</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-1127183.985621959</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>76003993</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>76003993.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>63.04</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>63.92</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>68.22</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>63.92</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>68.22</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>85385834.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>169884394.0</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>169884394</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>125724288.6</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>338045767.54</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>338045767.54</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>5698287.983461648</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>85385834</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>85385834.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29647,11 +29251,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
           <t>2459</t>
@@ -29833,41 +29433,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr">
         <is>
           <t>0</t>
@@ -29888,20 +29484,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>0</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>0</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29510,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>0</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29863,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29914,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29940,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>10702402903</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30109,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30293,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30344,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30370,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>9579043601</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30539,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30723,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30774,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30800,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>16911194399</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30969,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31153,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31204,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31230,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>15812987742</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31399,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31583,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31634,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31660,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>15882778006</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31829,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32013,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32064,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32090,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>10973548400</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32443,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32494,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32520,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>12353712685</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32689,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32873,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32924,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32950,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>10709769939</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33119,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33303,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33354,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33380,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>18182742782</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33549,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33733,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33784,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33810,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>10733728288</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33979,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34163,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34214,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34240,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>13958553198</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34409,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34593,11 @@
           <t>193.6</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>199.42</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>206.37</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>206.37</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34644,16 @@
           <t>103692746.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>118689542.8</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>118689542.8</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>168956434.6</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>210639255.6</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>210639255.6</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34670,10 @@
           <t>-21994999.89875582</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>103692746</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>103692746.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34839,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35023,11 @@
           <t>192.8</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>199.6</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>206.79</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>206.79</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35074,16 @@
           <t>83296686.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>132951227.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>132951227.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>187104254.0</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>216056658.14</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>216056658.14</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35100,10 @@
           <t>-21153128.92795646</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>83296686</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>83296686.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35269,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35453,11 @@
           <t>190.5</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>199.9</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>207.4</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>207.4</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35504,16 @@
           <t>61949648.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>158673800.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>158673800.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>190641450.0</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>221503976.62</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>221503976.62</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35530,10 @@
           <t>-17009695.07938755</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>61949648</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>61949648.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35699,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35883,11 @@
           <t>191.3</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>200.98</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>208.27</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>200.98</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>208.27</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35934,16 @@
           <t>171049391.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>185721656.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>185721656</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>194467502.8</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>225715579.68</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>225715579.68</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35960,10 @@
           <t>-8195832.11431092</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>171049391</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>171049391.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36129,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36313,11 @@
           <t>193.8</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>202.12</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>209.21</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>202.12</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>209.21</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36364,16 @@
           <t>173459243.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>214560702.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>214560702.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>190367255.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>229384096.36</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>229384096.36</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36390,10 @@
           <t>-7001149.195833266</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>173459243</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>173459243.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36559,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36743,11 @@
           <t>197.3</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>203.28</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>209.98</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>203.28</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>209.98</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36794,16 @@
           <t>175001170.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>219223326.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>219223326.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>198890553.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>237319445.14</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>237319445.14</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36820,10 @@
           <t>-5302616.698156834</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>175001170</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>175001170.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36989,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37173,11 @@
           <t>200.4</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>204.9</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>210.68</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>204.9</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>210.68</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37224,16 @@
           <t>211909550.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>241257280.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>241257280.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>195768003.1</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>243255926.66</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>243255926.66</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37250,10 @@
           <t>-2851968.997970581</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>211909550</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>211909550.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37419,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37603,11 @@
           <t>203.1</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>206.82</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>211.51</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>206.82</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>211.51</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37654,16 @@
           <t>197188926.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>222609099.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>222609099.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>192571153.1</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>247917131.98</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>247917131.98</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37680,10 @@
           <t>-3203656.962062716</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>197188926</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>197188926.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37849,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38033,11 @@
           <t>205.3</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>208.1</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>212.12</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>208.1</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>212.12</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38084,16 @@
           <t>315244622.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>203213349.6</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>203213349.6</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>184850244.1</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>256109616.18</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>256109616.18</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38110,10 @@
           <t>-2014442.304977804</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>315244622</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>315244622.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38279,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38463,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>209.5</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>212.87</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>212.87</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38514,16 @@
           <t>196772364.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>166173809.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>166173809</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>176703005.8</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>270755220.04</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>270755220.04</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38540,10 @@
           <t>-12892444.42682159</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>196772364</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>196772364.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38709,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38893,11 @@
           <t>204.9</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>209.5</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>213.68</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>213.68</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38944,16 @@
           <t>285170940.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>178557781.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>178557781.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>186036429.2</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>275437421.42</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>275437421.42</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>-15278546.79992619</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>285170940</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>285170940.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>176.35</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>178.66</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>178.66</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>237989780.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>367839281.4</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>367839281.4</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>390785616.2</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>619088599.9</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>619088599.9</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>-136007795.8903053</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>237989780</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>237989780.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>163.3</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>176.75</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>179.19</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>179.19</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>159879057.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>390309422.8</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>390309422.8</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>388711962.0</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>624204896.68</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>624204896.6799999</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>-136759988.5246557</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>159879057</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>159879057.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>163.2</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>177.4</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>179.87</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>179.87</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>281592910.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>454120103.0</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>454120103</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>408623891.0</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>634139495.34</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>634139495.34</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>-124581258.0907041</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>281592910</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>281592910.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>178.15</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>180.47</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>180.47</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>661439743.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>465917519.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>465917519</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>425236210.1</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>640116204.56</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>640116204.5599999</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>-115774511.0746768</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>661439743</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>661439743.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>165.8</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>178.8</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>181.02</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>181.02</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>498294917.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>454526412.0</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>454526412</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>417725808.9</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>631196639.66</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>631196639.66</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>-139756514.9062564</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>498294917</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>498294917.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>167.8</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>179.3</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>181.48</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>181.48</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>350340487.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>413731951.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>413731951</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>411216325.6</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>634370543.96</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>634370543.96</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>-151545413.4904325</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>350340487</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>350340487.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>170.7</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>179.98</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>182.09</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>182.09</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>478932458.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>387114501.2</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>387114501.2</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>473719052.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>647350541.68</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>647350541.6799999</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>-147122100.6288829</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>478932458</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>478932458.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>173.6</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>180.65</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>182.55</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>182.55</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>340579990.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>363127679.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>363127679</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>670451790.8</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>644918717.5</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>644918717.5</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>-149326432.6970662</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>340579990</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>340579990.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>175.7</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>181.12</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>182.92</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>181.12</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>182.92</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>604484208.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>384554901.2</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>384554901.2</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>1377596235.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>654170853.0</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>654170853</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>-132318912.9124327</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>604484208</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>604484208.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>177.8</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>181.55</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>183.34</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>183.34</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>294322612.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>380925205.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>380925205.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>1777576263.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>698405618.96</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>698405618.96</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>-131572232.5446552</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>294322612</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>294322612.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>179.8</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>181.42</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>183.81</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>183.81</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>217253238.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>408700700.2</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>408700700.2</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>1872522206.7</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>746966653.34</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>746966653.34</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>-92574938.4283781</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>217253238</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>217253238.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
